--- a/UTCUTS/A1_Outputs/previous_version_1/A-O_Demand_PREV1.xlsx
+++ b/UTCUTS/A1_Outputs/previous_version_1/A-O_Demand_PREV1.xlsx
@@ -4494,7 +4494,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50E219FA-873D-407A-BAF9-C890387D1211}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A98E94B-5922-488C-B61F-532B70B69F91}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
